--- a/SALT/FUNaK_AIMD.xlsx
+++ b/SALT/FUNaK_AIMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E4E9D-C8F7-B64B-8983-3AADCA6C6A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779FF839-80DC-0848-BA68-327D34874554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22800" yWindow="8540" windowWidth="27640" windowHeight="16940" xr2:uid="{508FF463-2D01-1741-9B5B-BF51988EC3F1}"/>
+    <workbookView xWindow="12980" yWindow="1940" windowWidth="27660" windowHeight="16960" xr2:uid="{508FF463-2D01-1741-9B5B-BF51988EC3F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
   <si>
     <t>FUNaK</t>
   </si>
@@ -142,9 +142,6 @@
   </si>
   <si>
     <t>plus/minus</t>
-  </si>
-  <si>
-    <t>50-25-25</t>
   </si>
   <si>
     <t>15000ps, averaging over last 2ps</t>
@@ -293,7 +290,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$44:$B$48</c:f>
+              <c:f>Sheet1!$B$64:$B$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -311,12 +308,12 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$J$44:$J$48</c:f>
+              <c:f>Sheet1!$J$64:$J$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.5446908918880267</c:v>
+                  <c:v>2.5386491434765497</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.3776558019268443</c:v>
@@ -613,7 +610,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$D$67:$D$71</c:f>
+              <c:f>Sheet1!$D$87:$D$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -631,7 +628,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$L$67:$L$71</c:f>
+              <c:f>Sheet1!$L$87:$L$91</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1960,13 +1957,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>679450</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1996,13 +1993,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2360,7 +2357,7 @@
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
@@ -2407,27 +2404,27 @@
         <v>1000</v>
       </c>
       <c r="C8">
-        <v>-131691.56596400001</v>
+        <v>-131691.34311399999</v>
       </c>
       <c r="D8">
-        <v>20.636737</v>
+        <v>20.564757</v>
       </c>
       <c r="E8">
-        <v>1004.105276</v>
+        <v>1000.603</v>
       </c>
       <c r="F8">
-        <v>-13.187897</v>
+        <v>21.638107000000002</v>
       </c>
       <c r="G8">
-        <v>3537.563142</v>
+        <v>3515.0775180000001</v>
       </c>
       <c r="I8">
         <f>C8+D8</f>
-        <v>-131670.92922700002</v>
+        <v>-131670.778357</v>
       </c>
       <c r="J8">
         <f>($F$20*(1.66E-24)/(G8*1E-24))</f>
-        <v>2.046153385663017</v>
+        <v>2.0592424385902266</v>
       </c>
       <c r="L8">
         <f>2.57-0.0006*B8</f>
@@ -2435,24 +2432,24 @@
       </c>
       <c r="M8">
         <f>ABS(J8-L8)/L8</f>
-        <v>3.8656540945694019E-2</v>
+        <v>4.5300730248846122E-2</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C9">
-        <v>1.470985</v>
+        <v>1.311693</v>
       </c>
       <c r="D9">
-        <v>1.3557170000000001</v>
+        <v>1.4260729999999999</v>
       </c>
       <c r="E9">
-        <v>65.964065000000005</v>
+        <v>69.387305999999995</v>
       </c>
       <c r="F9">
-        <v>321.77056099999999</v>
+        <v>331.02980200000002</v>
       </c>
       <c r="G9">
-        <v>61.595595000000003</v>
+        <v>68.792744999999996</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
@@ -2460,27 +2457,27 @@
         <v>1200</v>
       </c>
       <c r="C10">
-        <v>-131684.18872899999</v>
+        <v>-131683.83742900001</v>
       </c>
       <c r="D10">
-        <v>24.766245999999999</v>
+        <v>24.670059999999999</v>
       </c>
       <c r="E10">
-        <v>1205.0314699999999</v>
+        <v>1200.3514319999999</v>
       </c>
       <c r="F10">
-        <v>5.8192199999999996</v>
+        <v>-19.648733</v>
       </c>
       <c r="G10">
-        <v>3757.039092</v>
+        <v>3708.5340759999999</v>
       </c>
       <c r="I10">
         <f>C10+D10</f>
-        <v>-131659.42248299997</v>
+        <v>-131659.167369</v>
       </c>
       <c r="J10">
         <f>($F$20*(1.66E-24)/(G10*1E-24))</f>
-        <v>1.9266227001504939</v>
+        <v>1.9518215692943792</v>
       </c>
       <c r="L10">
         <f>2.57-0.0006*B10</f>
@@ -2488,24 +2485,24 @@
       </c>
       <c r="M10">
         <f>ABS(J10-L10)/L10</f>
-        <v>4.1417675757023785E-2</v>
+        <v>5.5038686105069928E-2</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C11">
-        <v>2.0310779999999999</v>
+        <v>1.750103</v>
       </c>
       <c r="D11">
-        <v>1.6665209999999999</v>
+        <v>1.68838</v>
       </c>
       <c r="E11">
-        <v>81.086591999999996</v>
+        <v>82.150160999999997</v>
       </c>
       <c r="F11">
-        <v>307.53830499999998</v>
+        <v>309.25984399999999</v>
       </c>
       <c r="G11">
-        <v>99.413413000000006</v>
+        <v>128.32722999999999</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
@@ -2513,27 +2510,27 @@
         <v>1400</v>
       </c>
       <c r="C12">
-        <v>-131676.286659</v>
+        <v>-131676.01136500001</v>
       </c>
       <c r="D12">
-        <v>28.888845</v>
+        <v>28.795093999999999</v>
       </c>
       <c r="E12">
-        <v>1405.621492</v>
+        <v>1401.0598990000001</v>
       </c>
       <c r="F12">
-        <v>-12.212116999999999</v>
+        <v>-10.373224</v>
       </c>
       <c r="G12">
-        <v>4029.4872070000001</v>
+        <v>4041.9310380000002</v>
       </c>
       <c r="I12">
         <f>C12+D12</f>
-        <v>-131647.397814</v>
+        <v>-131647.21627100001</v>
       </c>
       <c r="J12">
         <f>($F$20*(1.66E-24)/(G12*1E-24))</f>
-        <v>1.7963568136971628</v>
+        <v>1.790826397568043</v>
       </c>
       <c r="L12">
         <f>2.57-0.0006*B12</f>
@@ -2541,24 +2538,24 @@
       </c>
       <c r="M12">
         <f>ABS(J12-L12)/L12</f>
-        <v>3.8356539709342684E-2</v>
+        <v>3.5159767380371666E-2</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C13">
-        <v>2.1504479999999999</v>
+        <v>2.7010700000000001</v>
       </c>
       <c r="D13">
-        <v>1.878172</v>
+        <v>1.956507</v>
       </c>
       <c r="E13">
-        <v>91.384720000000002</v>
+        <v>95.196196</v>
       </c>
       <c r="F13">
-        <v>308.23584499999998</v>
+        <v>279.961522</v>
       </c>
       <c r="G13">
-        <v>121.462112</v>
+        <v>184.964361</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
@@ -2583,7 +2580,7 @@
         <v>1000</v>
       </c>
       <c r="I15">
-        <v>-131670.92922700002</v>
+        <v>-131670.778357</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
@@ -2608,7 +2605,7 @@
         <v>1200</v>
       </c>
       <c r="I16">
-        <v>-131659.42248299997</v>
+        <v>-131659.167369</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
@@ -2629,7 +2626,7 @@
         <v>1400</v>
       </c>
       <c r="I17">
-        <v>-131647.397814</v>
+        <v>-131647.21627100001</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
@@ -2663,10 +2660,10 @@
       </c>
       <c r="I19" cm="1">
         <f t="array" ref="I19:J19">LINEST(I15:I17,H15:H17)</f>
-        <v>5.8828532500047014E-2</v>
+        <v>5.8905214999977029E-2</v>
       </c>
       <c r="J19">
-        <v>-131729.84408033339</v>
+        <v>-131729.74025699997</v>
       </c>
       <c r="L19" t="s">
         <v>22</v>
@@ -2689,7 +2686,7 @@
       </c>
       <c r="I20">
         <f>I19/SUM(D15:D18)*(1.6E-19)*(6.022E+23)</f>
-        <v>70.853084543056625</v>
+        <v>70.945440945972337</v>
       </c>
       <c r="J20" t="s">
         <v>10</v>
@@ -2699,7 +2696,7 @@
       </c>
       <c r="M20">
         <f>ABS(I20-L20)/L20</f>
-        <v>6.2680989753628701E-3</v>
+        <v>4.9727777563486767E-3</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.2">
@@ -2902,7 +2899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33">
         <f>D33/SUM(D32:D35)</f>
         <v>0.5161290322580645</v>
@@ -2927,7 +2924,7 @@
         <v>-108946.604601</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34">
         <f>D34/SUM(D32:D35)</f>
         <v>3.2258064516129031E-2</v>
@@ -2952,7 +2949,7 @@
         <v>-108935.347423</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
         <v>14</v>
       </c>
@@ -2967,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
         <v>15</v>
       </c>
@@ -2989,7 +2986,7 @@
         <v>-109008.91975900004</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="D37">
         <f>SUM(D32:D36)</f>
         <v>130</v>
@@ -3009,7 +3006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="F38">
         <f>F37*1.66E-24</f>
         <v>6.0805468000000002E-21</v>
@@ -3018,664 +3015,569 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
+        <v>8</v>
+      </c>
+      <c r="I42" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>1000</v>
+      </c>
+      <c r="C43">
+        <v>-131578.70683099999</v>
+      </c>
+      <c r="D43">
+        <v>19.691800000000001</v>
+      </c>
+      <c r="E43">
+        <v>995.70188099999996</v>
+      </c>
+      <c r="F43">
+        <v>-57.350825999999998</v>
+      </c>
+      <c r="G43">
+        <v>2938.6032919999998</v>
+      </c>
+      <c r="I43">
+        <f>C43+D43</f>
+        <v>-131559.01503099999</v>
+      </c>
+      <c r="J43">
+        <f>($F$37*(1.66E-24)/(G43*1E-24))</f>
+        <v>2.069196211871664</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C44">
+        <v>1.633246</v>
+      </c>
+      <c r="D44">
+        <v>1.2799419999999999</v>
+      </c>
+      <c r="E44">
+        <v>64.719352999999998</v>
+      </c>
+      <c r="F44">
+        <v>494.627726</v>
+      </c>
+      <c r="G44">
+        <v>61.491624000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <v>1200</v>
+      </c>
+      <c r="I45">
+        <f>C45+D45</f>
+        <v>0</v>
+      </c>
+      <c r="J45" t="e">
+        <f>($F$37*(1.66E-24)/(G45*1E-24))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>1400</v>
+      </c>
+      <c r="I47">
+        <f>C47+D47</f>
+        <v>0</v>
+      </c>
+      <c r="J47" t="e">
+        <f>($F$37*(1.66E-24)/(G47*1E-24))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B50">
+        <f>D50/SUM(D50:D53)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50">
+        <v>28</v>
+      </c>
+      <c r="E50">
+        <v>22.99</v>
+      </c>
+      <c r="F50">
+        <f>D50*E50</f>
+        <v>643.71999999999991</v>
+      </c>
+      <c r="H50">
+        <v>1000</v>
+      </c>
+      <c r="I50">
+        <v>-108956.29340600001</v>
+      </c>
+      <c r="L50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <f>D51/SUM(D50:D53)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51">
+        <v>14</v>
+      </c>
+      <c r="E51">
+        <v>39.1</v>
+      </c>
+      <c r="F51">
+        <f t="shared" ref="F51" si="4">D51*E51</f>
+        <v>547.4</v>
+      </c>
+      <c r="H51">
+        <v>1200</v>
+      </c>
+      <c r="I51">
+        <v>-108946.604601</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <f>D52/SUM(D50:D53)</f>
+        <v>0.25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52">
+        <v>14</v>
+      </c>
+      <c r="E52">
+        <v>238.03</v>
+      </c>
+      <c r="F52">
+        <f>D52*E52</f>
+        <v>3332.42</v>
+      </c>
+      <c r="H52">
+        <v>1400</v>
+      </c>
+      <c r="I52">
+        <v>-108935.347423</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>91.22</v>
+      </c>
+      <c r="F53">
+        <f t="shared" ref="F53:F54" si="5">D53*E53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54">
+        <v>98</v>
+      </c>
+      <c r="E54">
+        <v>19</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="5"/>
+        <v>1862</v>
+      </c>
+      <c r="I54" cm="1">
+        <f t="array" ref="I54:J54">LINEST(I50:I52,H50:H52)</f>
+        <v>5.2364957500030868E-2</v>
+      </c>
+      <c r="J54">
+        <v>-109008.91975900004</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D55">
+        <f>SUM(D50:D54)</f>
+        <v>154</v>
+      </c>
+      <c r="F55">
+        <f>SUM(F50:F54)</f>
+        <v>6385.54</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55">
+        <f>I54/SUM(D50:D53)*(1.6E-19)*(6.022E+23)</f>
+        <v>90.097649732910241</v>
+      </c>
+      <c r="J55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F56">
+        <f>F55*1.66E-24</f>
+        <v>1.05999964E-20</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C63" t="s">
         <v>4</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D63" t="s">
         <v>5</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E63" t="s">
         <v>6</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F63" t="s">
         <v>7</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G63" t="s">
         <v>8</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I63" t="s">
         <v>9</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J63" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B64">
         <v>1000</v>
       </c>
-      <c r="C44">
-        <v>-130584.304281</v>
-      </c>
-      <c r="D44">
-        <v>20.624890000000001</v>
-      </c>
-      <c r="E44">
-        <v>1003.528827</v>
-      </c>
-      <c r="F44">
-        <v>6.7501360000000004</v>
-      </c>
-      <c r="G44">
-        <v>3277.583783</v>
-      </c>
-      <c r="I44">
-        <f>C44+D44</f>
+      <c r="C64">
+        <v>-130583.558621</v>
+      </c>
+      <c r="D64">
+        <v>20.550592999999999</v>
+      </c>
+      <c r="E64">
+        <v>999.913816</v>
+      </c>
+      <c r="F64">
+        <v>9.8993020000000005</v>
+      </c>
+      <c r="G64">
+        <v>3285.3841269999998</v>
+      </c>
+      <c r="I64">
+        <f>C64+D64</f>
+        <v>-130563.008028</v>
+      </c>
+      <c r="J64">
+        <f>($F$76*(1.66E-24)/(G64*1E-24))</f>
+        <v>2.5386491434765497</v>
+      </c>
+      <c r="K64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>1.5918350000000001</v>
+      </c>
+      <c r="D65">
+        <v>1.386547</v>
+      </c>
+      <c r="E65">
+        <v>67.464121000000006</v>
+      </c>
+      <c r="F65">
+        <v>417.94798700000001</v>
+      </c>
+      <c r="G65">
+        <v>52.693874999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B66">
+        <v>1200</v>
+      </c>
+      <c r="C66">
+        <v>-130576.795155</v>
+      </c>
+      <c r="D66">
+        <v>24.652607</v>
+      </c>
+      <c r="E66">
+        <v>1199.5022550000001</v>
+      </c>
+      <c r="F66">
+        <v>3.190788</v>
+      </c>
+      <c r="G66">
+        <v>3507.8406190000001</v>
+      </c>
+      <c r="I66">
+        <f>C66+D66</f>
+        <v>-130552.142548</v>
+      </c>
+      <c r="J66">
+        <f>($F$76*(1.66E-24)/(G66*1E-24))</f>
+        <v>2.3776558019268443</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>2.2433770000000002</v>
+      </c>
+      <c r="D67">
+        <v>1.6408480000000001</v>
+      </c>
+      <c r="E67">
+        <v>79.837434000000002</v>
+      </c>
+      <c r="F67">
+        <v>392.462715</v>
+      </c>
+      <c r="G67">
+        <v>113.36863099999999</v>
+      </c>
+      <c r="L67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>1400</v>
+      </c>
+      <c r="C68">
+        <v>-130573.13898</v>
+      </c>
+      <c r="D68">
+        <v>28.744634000000001</v>
+      </c>
+      <c r="E68">
+        <v>1398.604722</v>
+      </c>
+      <c r="F68">
+        <v>-5.3034109999999997</v>
+      </c>
+      <c r="G68">
+        <v>3743.43869</v>
+      </c>
+      <c r="I68">
+        <f>C68+D68</f>
+        <v>-130544.394346</v>
+      </c>
+      <c r="J68">
+        <f>($F$76*(1.66E-24)/(G68*1E-24))</f>
+        <v>2.2280150125819214</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C69">
+        <v>2.827788</v>
+      </c>
+      <c r="D69">
+        <v>1.9252590000000001</v>
+      </c>
+      <c r="E69">
+        <v>93.675785000000005</v>
+      </c>
+      <c r="F69">
+        <v>468.184304</v>
+      </c>
+      <c r="G69">
+        <v>124.96886600000001</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <f>D71/SUM(D71:D74)</f>
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71">
+        <v>24</v>
+      </c>
+      <c r="E71">
+        <v>22.99</v>
+      </c>
+      <c r="F71">
+        <f>D71*E71</f>
+        <v>551.76</v>
+      </c>
+      <c r="H71">
+        <v>1000</v>
+      </c>
+      <c r="I71">
         <v>-130563.679391</v>
       </c>
-      <c r="J44">
-        <f>($F$56*(1.66E-24)/(G44*1E-24))</f>
-        <v>2.5446908918880267</v>
-      </c>
-      <c r="K44" t="s">
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <f>D72/SUM(D71:D74)</f>
+        <v>0.52941176470588236</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72">
+        <v>36</v>
+      </c>
+      <c r="E72">
+        <v>39.1</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ref="F72:F75" si="6">D72*E72</f>
+        <v>1407.6000000000001</v>
+      </c>
+      <c r="H72">
+        <v>1200</v>
+      </c>
+      <c r="I72">
+        <v>-130552.142548</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <f>D73/SUM(D71:D74)</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73">
+        <v>238.03</v>
+      </c>
+      <c r="F73">
+        <f>D73*E73</f>
+        <v>952.12</v>
+      </c>
+      <c r="H73">
+        <v>1400</v>
+      </c>
+      <c r="I73">
+        <v>-130544.394346</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <f>D74/SUM(D71:D74)</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>91.22</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="6"/>
+        <v>364.88</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75">
+        <v>92</v>
+      </c>
+      <c r="E75">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C45">
-        <v>1.4253610000000001</v>
-      </c>
-      <c r="D45">
-        <v>1.3872249999999999</v>
-      </c>
-      <c r="E45">
-        <v>67.497083000000003</v>
-      </c>
-      <c r="F45">
-        <v>422.60334</v>
-      </c>
-      <c r="G45">
-        <v>69.661548999999994</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46">
-        <v>1200</v>
-      </c>
-      <c r="C46">
-        <v>-130576.795155</v>
-      </c>
-      <c r="D46">
-        <v>24.652607</v>
-      </c>
-      <c r="E46">
-        <v>1199.5022550000001</v>
-      </c>
-      <c r="F46">
-        <v>3.190788</v>
-      </c>
-      <c r="G46">
-        <v>3507.8406190000001</v>
-      </c>
-      <c r="I46">
-        <f>C46+D46</f>
-        <v>-130552.142548</v>
-      </c>
-      <c r="J46">
-        <f>($F$56*(1.66E-24)/(G46*1E-24))</f>
-        <v>2.3776558019268443</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C47">
-        <v>2.2433770000000002</v>
-      </c>
-      <c r="D47">
-        <v>1.6408480000000001</v>
-      </c>
-      <c r="E47">
-        <v>79.837434000000002</v>
-      </c>
-      <c r="F47">
-        <v>392.462715</v>
-      </c>
-      <c r="G47">
-        <v>113.36863099999999</v>
-      </c>
-      <c r="L47" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>1400</v>
-      </c>
-      <c r="C48">
-        <v>-130573.13898</v>
-      </c>
-      <c r="D48">
-        <v>28.744634000000001</v>
-      </c>
-      <c r="E48">
-        <v>1398.604722</v>
-      </c>
-      <c r="F48">
-        <v>-5.3034109999999997</v>
-      </c>
-      <c r="G48">
-        <v>3743.43869</v>
-      </c>
-      <c r="I48">
-        <f>C48+D48</f>
-        <v>-130544.394346</v>
-      </c>
-      <c r="J48">
-        <f>($F$56*(1.66E-24)/(G48*1E-24))</f>
-        <v>2.2280150125819214</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C49">
-        <v>2.827788</v>
-      </c>
-      <c r="D49">
-        <v>1.9252590000000001</v>
-      </c>
-      <c r="E49">
-        <v>93.675785000000005</v>
-      </c>
-      <c r="F49">
-        <v>468.184304</v>
-      </c>
-      <c r="G49">
-        <v>124.96886600000001</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B51">
-        <f>D51/SUM(D51:D54)</f>
-        <v>0.35294117647058826</v>
-      </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51">
-        <v>24</v>
-      </c>
-      <c r="E51">
-        <v>22.99</v>
-      </c>
-      <c r="F51">
-        <f>D51*E51</f>
-        <v>551.76</v>
-      </c>
-      <c r="H51">
-        <v>1000</v>
-      </c>
-      <c r="I51">
-        <v>-130563.679391</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <f>D52/SUM(D51:D54)</f>
-        <v>0.52941176470588236</v>
-      </c>
-      <c r="C52" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52">
-        <v>36</v>
-      </c>
-      <c r="E52">
-        <v>39.1</v>
-      </c>
-      <c r="F52">
-        <f t="shared" ref="F52:F55" si="4">D52*E52</f>
-        <v>1407.6000000000001</v>
-      </c>
-      <c r="H52">
-        <v>1200</v>
-      </c>
-      <c r="I52">
-        <v>-130552.142548</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <f>D53/SUM(D51:D54)</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53">
-        <v>4</v>
-      </c>
-      <c r="E53">
-        <v>238.03</v>
-      </c>
-      <c r="F53">
-        <f>D53*E53</f>
-        <v>952.12</v>
-      </c>
-      <c r="H53">
-        <v>1400</v>
-      </c>
-      <c r="I53">
-        <v>-130544.394346</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B54">
-        <f>D54/SUM(D51:D54)</f>
-        <v>5.8823529411764705E-2</v>
-      </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54">
-        <v>4</v>
-      </c>
-      <c r="E54">
-        <v>91.22</v>
-      </c>
-      <c r="F54">
-        <f t="shared" si="4"/>
-        <v>364.88</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C55" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55">
-        <v>92</v>
-      </c>
-      <c r="E55">
-        <v>19</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="4"/>
+      <c r="F75">
+        <f t="shared" si="6"/>
         <v>1748</v>
       </c>
-      <c r="I55" cm="1">
-        <f t="array" ref="I55:J55">LINEST(I51:I53,H51:H53)</f>
+      <c r="I75" cm="1">
+        <f t="array" ref="I75:J75">LINEST(I71:I73,H71:H73)</f>
         <v>4.8212612499992258E-2</v>
       </c>
-      <c r="J55">
+      <c r="J75">
         <v>-130611.26056333332</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D56">
-        <f>SUM(D51:D55)</f>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D76">
+        <f>SUM(D71:D75)</f>
         <v>160</v>
       </c>
-      <c r="F56">
-        <f>SUM(F51:F55)</f>
+      <c r="F76">
+        <f>SUM(F71:F75)</f>
         <v>5024.3600000000006</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G76" t="s">
         <v>16</v>
       </c>
-      <c r="I56">
-        <f>I55/SUM(D51:D54)*(1.6E-19)*(6.022E+23)</f>
+      <c r="I76">
+        <f>I75/SUM(D71:D74)*(1.6E-19)*(6.022E+23)</f>
         <v>68.314435876459626</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J76" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="F57">
-        <f>F56*1.66E-24</f>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F77">
+        <f>F76*1.66E-24</f>
         <v>8.3404376000000016E-21</v>
       </c>
-      <c r="G57" t="s">
+      <c r="G77" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B65" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E66" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" t="s">
-        <v>6</v>
-      </c>
-      <c r="H66" t="s">
-        <v>7</v>
-      </c>
-      <c r="I66" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" t="s">
-        <v>9</v>
-      </c>
-      <c r="L66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-      <c r="D67">
-        <v>1000</v>
-      </c>
-      <c r="E67">
-        <v>-141157.172682</v>
-      </c>
-      <c r="F67">
-        <v>22.069399000000001</v>
-      </c>
-      <c r="G67">
-        <v>998.45782399999996</v>
-      </c>
-      <c r="H67">
-        <v>-25.111764999999998</v>
-      </c>
-      <c r="I67">
-        <v>3330.4469290000002</v>
-      </c>
-      <c r="K67">
-        <f>E67+F67</f>
-        <v>-141135.103283</v>
-      </c>
-      <c r="L67">
-        <f>($H$79*(1.66E-24)/(I67*1E-24))</f>
-        <v>2.7550906516787195</v>
-      </c>
-      <c r="M67" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E68">
-        <v>1.371667</v>
-      </c>
-      <c r="F68">
-        <v>1.376177</v>
-      </c>
-      <c r="G68">
-        <v>62.260638999999998</v>
-      </c>
-      <c r="H68">
-        <v>522.68107299999997</v>
-      </c>
-      <c r="I68">
-        <v>76.299685999999994</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D69">
-        <v>1200</v>
-      </c>
-      <c r="E69">
-        <v>-141151.34962299999</v>
-      </c>
-      <c r="F69">
-        <v>26.354557</v>
-      </c>
-      <c r="G69">
-        <v>1192.325789</v>
-      </c>
-      <c r="H69">
-        <v>-31.510287999999999</v>
-      </c>
-      <c r="I69">
-        <v>3519.3794039999998</v>
-      </c>
-      <c r="K69">
-        <f>E69+F69</f>
-        <v>-141124.99506599997</v>
-      </c>
-      <c r="L69">
-        <f>($H$79*(1.66E-24)/(I69*1E-24))</f>
-        <v>2.60718784384862</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E70">
-        <v>2.1367660000000002</v>
-      </c>
-      <c r="F70">
-        <v>1.5799589999999999</v>
-      </c>
-      <c r="G70">
-        <v>71.480069999999998</v>
-      </c>
-      <c r="H70">
-        <v>581.02007600000002</v>
-      </c>
-      <c r="I70">
-        <v>135.36157800000001</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D71">
-        <v>1400</v>
-      </c>
-      <c r="E71">
-        <v>-141143.59498699999</v>
-      </c>
-      <c r="F71">
-        <v>30.773126999999999</v>
-      </c>
-      <c r="G71">
-        <v>1392.2295429999999</v>
-      </c>
-      <c r="H71">
-        <v>-7.3851699999999996</v>
-      </c>
-      <c r="I71">
-        <v>3766.8877299999999</v>
-      </c>
-      <c r="K71">
-        <f>E71+F71</f>
-        <v>-141112.82186</v>
-      </c>
-      <c r="L71">
-        <f>($H$79*(1.66E-24)/(I71*1E-24))</f>
-        <v>2.4358791282584895</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E72">
-        <v>2.183942</v>
-      </c>
-      <c r="F72">
-        <v>1.9108940000000001</v>
-      </c>
-      <c r="G72">
-        <v>86.452156000000002</v>
-      </c>
-      <c r="H72">
-        <v>601.82682699999998</v>
-      </c>
-      <c r="I72">
-        <v>128.87987000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D74">
-        <f>F74/SUM(F74:F77)</f>
-        <v>0.36</v>
-      </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74">
-        <v>18</v>
-      </c>
-      <c r="G74">
-        <v>22.99</v>
-      </c>
-      <c r="H74">
-        <f>F74*G74</f>
-        <v>413.82</v>
-      </c>
-      <c r="J74">
-        <v>1000</v>
-      </c>
-      <c r="K74">
-        <v>-141135.103283</v>
-      </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D75">
-        <f>F75/SUM(F74:F77)</f>
-        <v>0.16</v>
-      </c>
-      <c r="E75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75">
-        <v>8</v>
-      </c>
-      <c r="G75">
-        <v>39.1</v>
-      </c>
-      <c r="H75">
-        <f t="shared" ref="H75:H78" si="5">F75*G75</f>
-        <v>312.8</v>
-      </c>
-      <c r="J75">
-        <v>1200</v>
-      </c>
-      <c r="K75">
-        <v>-141124.99506599997</v>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D76">
-        <f>F76/SUM(F74:F77)</f>
-        <v>0.04</v>
-      </c>
-      <c r="E76" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76">
-        <v>2</v>
-      </c>
-      <c r="G76">
-        <v>238.03</v>
-      </c>
-      <c r="H76">
-        <f>F76*G76</f>
-        <v>476.06</v>
-      </c>
-      <c r="J76">
-        <v>1400</v>
-      </c>
-      <c r="K76">
-        <v>-141112.82186</v>
-      </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="D77">
-        <f>F77/SUM(F74:F77)</f>
-        <v>0.44</v>
-      </c>
-      <c r="E77" t="s">
-        <v>14</v>
-      </c>
-      <c r="F77">
-        <v>22</v>
-      </c>
-      <c r="G77">
-        <v>91.22</v>
-      </c>
-      <c r="H77">
-        <f t="shared" ref="H77:H80" si="6">F77*G77</f>
-        <v>2006.84</v>
-      </c>
-    </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78">
-        <v>122</v>
-      </c>
-      <c r="G78">
-        <v>19</v>
-      </c>
-      <c r="H78">
-        <f t="shared" si="6"/>
-        <v>2318</v>
-      </c>
-      <c r="K78" cm="1">
-        <f t="array" ref="K78:L78">LINEST(K74:K76,J74:J76)</f>
-        <v>5.5703557500019089E-2</v>
-      </c>
-      <c r="L78">
-        <v>-141191.15100533335</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="F79">
-        <f>SUM(F74:F78)</f>
-        <v>172</v>
-      </c>
-      <c r="H79">
-        <f>SUM(H74:H78)</f>
-        <v>5527.52</v>
-      </c>
-      <c r="I79" t="s">
-        <v>16</v>
-      </c>
-      <c r="K79">
-        <f>K78/SUM(F74:F77)*(1.6E-19)*(6.022E+23)</f>
-        <v>107.34298344483678</v>
-      </c>
-      <c r="L79" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H80">
-        <f>H79*1.66E-24</f>
-        <v>9.1756832000000005E-21</v>
-      </c>
-      <c r="I80" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K81" t="s">
-        <v>20</v>
-      </c>
-      <c r="L81" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K82">
-        <v>115</v>
-      </c>
-      <c r="L82">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K83">
-        <v>117</v>
-      </c>
-      <c r="L83">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E86" t="s">
         <v>4</v>
       </c>
@@ -3698,9 +3600,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D87">
         <v>1000</v>
@@ -3725,11 +3627,14 @@
         <v>-141135.103283</v>
       </c>
       <c r="L87">
-        <f>($H$79*(1.66E-24)/(I87*1E-24))</f>
+        <f>($H$99*(1.66E-24)/(I87*1E-24))</f>
         <v>2.7550906516787195</v>
       </c>
-    </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E88">
         <v>1.371667</v>
       </c>
@@ -3746,7 +3651,7 @@
         <v>76.299685999999994</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D89">
         <v>1200</v>
       </c>
@@ -3770,11 +3675,11 @@
         <v>-141124.99506599997</v>
       </c>
       <c r="L89">
-        <f>($H$79*(1.66E-24)/(I89*1E-24))</f>
+        <f>($H$99*(1.66E-24)/(I89*1E-24))</f>
         <v>2.60718784384862</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E90">
         <v>2.1367660000000002</v>
       </c>
@@ -3791,7 +3696,7 @@
         <v>135.36157800000001</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D91">
         <v>1400</v>
       </c>
@@ -3815,11 +3720,11 @@
         <v>-141112.82186</v>
       </c>
       <c r="L91">
-        <f>($H$79*(1.66E-24)/(I91*1E-24))</f>
+        <f>($H$99*(1.66E-24)/(I91*1E-24))</f>
         <v>2.4358791282584895</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
       <c r="E92">
         <v>2.183942</v>
       </c>
@@ -3836,7 +3741,7 @@
         <v>128.87987000000001</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D94">
         <f>F94/SUM(F94:F97)</f>
         <v>0.36</v>
@@ -3861,7 +3766,7 @@
         <v>-141135.103283</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D95">
         <f>F95/SUM(F94:F97)</f>
         <v>0.16</v>
@@ -3876,7 +3781,7 @@
         <v>39.1</v>
       </c>
       <c r="H95">
-        <f t="shared" ref="H95:H98" si="7">F95*G95</f>
+        <f t="shared" ref="H95" si="7">F95*G95</f>
         <v>312.8</v>
       </c>
       <c r="J95">
@@ -3886,7 +3791,7 @@
         <v>-141124.99506599997</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
       <c r="D96">
         <f>F96/SUM(F94:F97)</f>
         <v>0.04</v>
@@ -3926,7 +3831,7 @@
         <v>91.22</v>
       </c>
       <c r="H97">
-        <f t="shared" ref="H97:H100" si="8">F97*G97</f>
+        <f t="shared" ref="H97:H98" si="8">F97*G97</f>
         <v>2006.84</v>
       </c>
     </row>
